--- a/uploads/student-bank.xlsx
+++ b/uploads/student-bank.xlsx
@@ -1,146 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\limon\OneDrive\Desktop\Work\game\uploads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB20408F-C114-4C18-94B3-C5EAA0F8B172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="33120" yWindow="1035" windowWidth="23910" windowHeight="14835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="38">
-  <si>
-    <t>roll</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>session</t>
-  </si>
-  <si>
-    <t>class</t>
-  </si>
-  <si>
-    <t>section</t>
-  </si>
-  <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>isPresent</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>Abdullah Al Noman</t>
-  </si>
-  <si>
-    <t>STU2024001</t>
-  </si>
-  <si>
-    <t>2024-25</t>
-  </si>
-  <si>
-    <t>Eleven</t>
-  </si>
-  <si>
-    <t>Teesta</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>Rafiqul Islam</t>
-  </si>
-  <si>
-    <t>STU2024002</t>
-  </si>
-  <si>
-    <t>Twelve</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>Mahmud Hasan</t>
-  </si>
-  <si>
-    <t>STU2024004</t>
-  </si>
-  <si>
-    <t>Karnaphuli</t>
-  </si>
-  <si>
-    <t>Abdullah Al Amin</t>
-  </si>
-  <si>
-    <t>STU2024005</t>
-  </si>
-  <si>
-    <t>2025-26</t>
-  </si>
-  <si>
-    <t>Turag</t>
-  </si>
-  <si>
-    <t>526</t>
-  </si>
-  <si>
-    <t>Rabeya Akbor</t>
-  </si>
-  <si>
-    <t>STU2024006</t>
-  </si>
-  <si>
-    <t>Titash</t>
-  </si>
-  <si>
-    <t>Muhammad bin Abdullah</t>
-  </si>
-  <si>
-    <t>STU2024007</t>
-  </si>
-  <si>
-    <t>Chitra</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>Muhammad Abdullah</t>
-  </si>
-  <si>
-    <t>STU2024008</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -177,14 +72,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -509,60 +396,65 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K10"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>roll</v>
+      </c>
+      <c r="B1" t="str">
+        <v>name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>id</v>
+      </c>
+      <c r="D1" t="str">
+        <v>session</v>
+      </c>
+      <c r="E1" t="str">
+        <v>class</v>
+      </c>
+      <c r="F1" t="str">
+        <v>section</v>
+      </c>
+      <c r="G1" t="str">
+        <v>group</v>
+      </c>
+      <c r="H1" t="str">
+        <v>date</v>
+      </c>
+      <c r="I1" t="str">
+        <v>isPresent</v>
+      </c>
+      <c r="J1" t="str">
+        <v>mobile</v>
+      </c>
+      <c r="K1" t="str">
+        <v>gender</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>101</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Abdullah Al Noman</v>
+      </c>
+      <c r="C2" t="str">
+        <v>STU2024001</v>
+      </c>
+      <c r="D2" t="str">
+        <v>2024-25</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Eleven</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Teesta</v>
+      </c>
+      <c r="G2" t="str">
+        <v>A</v>
       </c>
       <c r="H2">
         <v>46178</v>
@@ -571,27 +463,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>15</v>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>102</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Rafiqul Islam</v>
+      </c>
+      <c r="C3" t="str">
+        <v>STU2024002</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2024-25</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Twelve</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Teesta</v>
+      </c>
+      <c r="G3" t="str">
+        <v>A</v>
       </c>
       <c r="H3">
         <v>46178</v>
@@ -600,27 +492,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" t="s">
-        <v>15</v>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>104</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Mahmud Hasan</v>
+      </c>
+      <c r="C4" t="str">
+        <v>STU2024004</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2024-25</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Twelve</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Karnaphuli</v>
+      </c>
+      <c r="G4" t="str">
+        <v>A</v>
       </c>
       <c r="H4">
         <v>46178</v>
@@ -629,27 +521,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5">
         <v>304</v>
       </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" t="s">
-        <v>15</v>
+      <c r="B5" t="str">
+        <v>Abdullah Al Amin</v>
+      </c>
+      <c r="C5" t="str">
+        <v>STU2024005</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2025-26</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Twelve</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Turag</v>
+      </c>
+      <c r="G5" t="str">
+        <v>A</v>
       </c>
       <c r="H5">
         <v>46178</v>
@@ -658,27 +550,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" t="s">
-        <v>15</v>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>526</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Rabeya Akbor</v>
+      </c>
+      <c r="C6" t="str">
+        <v>STU2024006</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2025-26</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Twelve</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Titash</v>
+      </c>
+      <c r="G6" t="str">
+        <v>A</v>
       </c>
       <c r="H6">
         <v>46178</v>
@@ -687,27 +579,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7">
         <v>556</v>
       </c>
-      <c r="B7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" t="s">
-        <v>35</v>
+      <c r="B7" t="str">
+        <v>Muhammad bin Abdullah</v>
+      </c>
+      <c r="C7" t="str">
+        <v>STU2024007</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2025-26</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Eleven</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Chitra</v>
+      </c>
+      <c r="G7" t="str">
+        <v>C</v>
       </c>
       <c r="H7">
         <v>46178</v>
@@ -716,27 +608,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8">
         <v>554</v>
       </c>
-      <c r="B8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" t="s">
-        <v>35</v>
+      <c r="B8" t="str">
+        <v>Muhammad Abdullah</v>
+      </c>
+      <c r="C8" t="str">
+        <v>STU2024008</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2025-26</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Eleven</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Chitra</v>
+      </c>
+      <c r="G8" t="str">
+        <v>C</v>
       </c>
       <c r="H8">
         <v>46178</v>
@@ -745,10 +637,67 @@
         <v>1</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>557</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Karim khan</v>
+      </c>
+      <c r="C9" t="str">
+        <v>STU2024008</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2024-25</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Eleven</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Karnaphuli</v>
+      </c>
+      <c r="G9" t="str">
+        <v>A</v>
+      </c>
+      <c r="J9" t="str">
+        <v>01711000001</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Male</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>558</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Rahim Mondol</v>
+      </c>
+      <c r="C10" t="str">
+        <v>STU2024009</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2025-26</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Twelve</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Shitalakhya</v>
+      </c>
+      <c r="G10" t="str">
+        <v>A</v>
+      </c>
+      <c r="J10" t="str">
+        <v>01851544333</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Male</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I6 C8:I8 C7:I7" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/uploads/student-bank.xlsx
+++ b/uploads/student-bank.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H510"/>
+  <dimension ref="A1:I516"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,6 +424,9 @@
       <c r="H1" t="str">
         <v>gender</v>
       </c>
+      <c r="I1" t="str">
+        <v>mobile</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -13659,9 +13662,183 @@
         <v>Male</v>
       </c>
     </row>
+    <row r="511">
+      <c r="A511" t="str">
+        <v>251177</v>
+      </c>
+      <c r="B511" t="str">
+        <v>659</v>
+      </c>
+      <c r="C511" t="str">
+        <v>MARUF AHMED</v>
+      </c>
+      <c r="D511" t="str">
+        <v>2025-26</v>
+      </c>
+      <c r="E511" t="str">
+        <v>Eleven</v>
+      </c>
+      <c r="F511" t="str">
+        <v>Jamuna</v>
+      </c>
+      <c r="G511" t="str">
+        <v>Science</v>
+      </c>
+      <c r="H511" t="str">
+        <v>Male</v>
+      </c>
+      <c r="I511" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="str">
+        <v>251147</v>
+      </c>
+      <c r="B512" t="str">
+        <v>670</v>
+      </c>
+      <c r="C512" t="str">
+        <v>MST. MONNI AKTER</v>
+      </c>
+      <c r="D512" t="str">
+        <v>2025-26</v>
+      </c>
+      <c r="E512" t="str">
+        <v>Eleven</v>
+      </c>
+      <c r="F512" t="str">
+        <v>Jamuna</v>
+      </c>
+      <c r="G512" t="str">
+        <v>Science</v>
+      </c>
+      <c r="H512" t="str">
+        <v>Female</v>
+      </c>
+      <c r="I512" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="str">
+        <v>251155</v>
+      </c>
+      <c r="B513" t="str">
+        <v>672</v>
+      </c>
+      <c r="C513" t="str">
+        <v>TAJMIN AKTER</v>
+      </c>
+      <c r="D513" t="str">
+        <v>2025-26</v>
+      </c>
+      <c r="E513" t="str">
+        <v>Eleven</v>
+      </c>
+      <c r="F513" t="str">
+        <v>Jamuna</v>
+      </c>
+      <c r="G513" t="str">
+        <v>Science</v>
+      </c>
+      <c r="H513" t="str">
+        <v>Female</v>
+      </c>
+      <c r="I513" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="str">
+        <v>251351</v>
+      </c>
+      <c r="B514" t="str">
+        <v>682</v>
+      </c>
+      <c r="C514" t="str">
+        <v>KHADIZA AKTER MIM</v>
+      </c>
+      <c r="D514" t="str">
+        <v>2025-26</v>
+      </c>
+      <c r="E514" t="str">
+        <v>Eleven</v>
+      </c>
+      <c r="F514" t="str">
+        <v>Jamuna</v>
+      </c>
+      <c r="G514" t="str">
+        <v>Science</v>
+      </c>
+      <c r="H514" t="str">
+        <v>Female</v>
+      </c>
+      <c r="I514" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="str">
+        <v>250697</v>
+      </c>
+      <c r="B515" t="str">
+        <v>902</v>
+      </c>
+      <c r="C515" t="str">
+        <v>MAHFUZA AKTER MIM</v>
+      </c>
+      <c r="D515" t="str">
+        <v>2025-26</v>
+      </c>
+      <c r="E515" t="str">
+        <v>Eleven</v>
+      </c>
+      <c r="F515" t="str">
+        <v>Karnaphuli</v>
+      </c>
+      <c r="G515" t="str">
+        <v>Humanities</v>
+      </c>
+      <c r="H515" t="str">
+        <v>Female</v>
+      </c>
+      <c r="I515" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="str">
+        <v>251288</v>
+      </c>
+      <c r="B516" t="str">
+        <v>960</v>
+      </c>
+      <c r="C516" t="str">
+        <v>JEHAD AHMED</v>
+      </c>
+      <c r="D516" t="str">
+        <v>2025-26</v>
+      </c>
+      <c r="E516" t="str">
+        <v>Eleven</v>
+      </c>
+      <c r="F516" t="str">
+        <v>Karnaphuli</v>
+      </c>
+      <c r="G516" t="str">
+        <v>Humanities</v>
+      </c>
+      <c r="H516" t="str">
+        <v>Male</v>
+      </c>
+      <c r="I516" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H510"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I516"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/uploads/student-bank.xlsx
+++ b/uploads/student-bank.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I516"/>
+  <dimension ref="A1:I527"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3331,7 +3331,7 @@
         <v>Twelve</v>
       </c>
       <c r="F113" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G113" t="str">
         <v>Humanities</v>
@@ -3357,7 +3357,7 @@
         <v>Twelve</v>
       </c>
       <c r="F114" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G114" t="str">
         <v>Humanities</v>
@@ -3383,7 +3383,7 @@
         <v>Twelve</v>
       </c>
       <c r="F115" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G115" t="str">
         <v>Humanities</v>
@@ -3409,7 +3409,7 @@
         <v>Twelve</v>
       </c>
       <c r="F116" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G116" t="str">
         <v>Humanities</v>
@@ -3435,7 +3435,7 @@
         <v>Twelve</v>
       </c>
       <c r="F117" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G117" t="str">
         <v>Humanities</v>
@@ -3461,7 +3461,7 @@
         <v>Twelve</v>
       </c>
       <c r="F118" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G118" t="str">
         <v>Humanities</v>
@@ -3487,7 +3487,7 @@
         <v>Twelve</v>
       </c>
       <c r="F119" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G119" t="str">
         <v>Humanities</v>
@@ -3513,7 +3513,7 @@
         <v>Twelve</v>
       </c>
       <c r="F120" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G120" t="str">
         <v>Humanities</v>
@@ -3539,7 +3539,7 @@
         <v>Twelve</v>
       </c>
       <c r="F121" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G121" t="str">
         <v>Humanities</v>
@@ -3565,7 +3565,7 @@
         <v>Twelve</v>
       </c>
       <c r="F122" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G122" t="str">
         <v>Humanities</v>
@@ -3591,7 +3591,7 @@
         <v>Twelve</v>
       </c>
       <c r="F123" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G123" t="str">
         <v>Humanities</v>
@@ -3617,7 +3617,7 @@
         <v>Twelve</v>
       </c>
       <c r="F124" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G124" t="str">
         <v>Humanities</v>
@@ -3643,7 +3643,7 @@
         <v>Twelve</v>
       </c>
       <c r="F125" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G125" t="str">
         <v>Humanities</v>
@@ -3669,7 +3669,7 @@
         <v>Twelve</v>
       </c>
       <c r="F126" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G126" t="str">
         <v>Humanities</v>
@@ -3695,7 +3695,7 @@
         <v>Twelve</v>
       </c>
       <c r="F127" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G127" t="str">
         <v>Humanities</v>
@@ -3721,7 +3721,7 @@
         <v>Twelve</v>
       </c>
       <c r="F128" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G128" t="str">
         <v>Humanities</v>
@@ -3747,7 +3747,7 @@
         <v>Twelve</v>
       </c>
       <c r="F129" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G129" t="str">
         <v>Humanities</v>
@@ -3773,7 +3773,7 @@
         <v>Twelve</v>
       </c>
       <c r="F130" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G130" t="str">
         <v>Humanities</v>
@@ -3799,7 +3799,7 @@
         <v>Twelve</v>
       </c>
       <c r="F131" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G131" t="str">
         <v>Humanities</v>
@@ -3825,7 +3825,7 @@
         <v>Twelve</v>
       </c>
       <c r="F132" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G132" t="str">
         <v>Humanities</v>
@@ -3851,7 +3851,7 @@
         <v>Twelve</v>
       </c>
       <c r="F133" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G133" t="str">
         <v>Humanities</v>
@@ -3877,7 +3877,7 @@
         <v>Twelve</v>
       </c>
       <c r="F134" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G134" t="str">
         <v>Humanities</v>
@@ -3903,7 +3903,7 @@
         <v>Twelve</v>
       </c>
       <c r="F135" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G135" t="str">
         <v>Humanities</v>
@@ -3929,7 +3929,7 @@
         <v>Twelve</v>
       </c>
       <c r="F136" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G136" t="str">
         <v>Humanities</v>
@@ -3955,7 +3955,7 @@
         <v>Twelve</v>
       </c>
       <c r="F137" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G137" t="str">
         <v>Humanities</v>
@@ -3981,7 +3981,7 @@
         <v>Twelve</v>
       </c>
       <c r="F138" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G138" t="str">
         <v>Humanities</v>
@@ -4007,7 +4007,7 @@
         <v>Twelve</v>
       </c>
       <c r="F139" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G139" t="str">
         <v>Humanities</v>
@@ -4033,7 +4033,7 @@
         <v>Twelve</v>
       </c>
       <c r="F140" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G140" t="str">
         <v>Humanities</v>
@@ -4059,7 +4059,7 @@
         <v>Twelve</v>
       </c>
       <c r="F141" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G141" t="str">
         <v>Humanities</v>
@@ -4085,7 +4085,7 @@
         <v>Twelve</v>
       </c>
       <c r="F142" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G142" t="str">
         <v>Humanities</v>
@@ -4111,7 +4111,7 @@
         <v>Twelve</v>
       </c>
       <c r="F143" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G143" t="str">
         <v>Humanities</v>
@@ -4137,7 +4137,7 @@
         <v>Twelve</v>
       </c>
       <c r="F144" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G144" t="str">
         <v>Humanities</v>
@@ -4163,7 +4163,7 @@
         <v>Twelve</v>
       </c>
       <c r="F145" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G145" t="str">
         <v>Humanities</v>
@@ -4189,7 +4189,7 @@
         <v>Twelve</v>
       </c>
       <c r="F146" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G146" t="str">
         <v>Humanities</v>
@@ -4215,7 +4215,7 @@
         <v>Twelve</v>
       </c>
       <c r="F147" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G147" t="str">
         <v>Humanities</v>
@@ -4241,7 +4241,7 @@
         <v>Twelve</v>
       </c>
       <c r="F148" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G148" t="str">
         <v>Humanities</v>
@@ -4267,7 +4267,7 @@
         <v>Twelve</v>
       </c>
       <c r="F149" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G149" t="str">
         <v>Humanities</v>
@@ -4293,7 +4293,7 @@
         <v>Twelve</v>
       </c>
       <c r="F150" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G150" t="str">
         <v>Humanities</v>
@@ -4319,7 +4319,7 @@
         <v>Twelve</v>
       </c>
       <c r="F151" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G151" t="str">
         <v>Humanities</v>
@@ -4345,7 +4345,7 @@
         <v>Twelve</v>
       </c>
       <c r="F152" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G152" t="str">
         <v>Humanities</v>
@@ -4371,7 +4371,7 @@
         <v>Twelve</v>
       </c>
       <c r="F153" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G153" t="str">
         <v>Humanities</v>
@@ -4397,7 +4397,7 @@
         <v>Twelve</v>
       </c>
       <c r="F154" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G154" t="str">
         <v>Humanities</v>
@@ -4423,7 +4423,7 @@
         <v>Twelve</v>
       </c>
       <c r="F155" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G155" t="str">
         <v>Humanities</v>
@@ -4449,7 +4449,7 @@
         <v>Twelve</v>
       </c>
       <c r="F156" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G156" t="str">
         <v>Humanities</v>
@@ -4475,7 +4475,7 @@
         <v>Twelve</v>
       </c>
       <c r="F157" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G157" t="str">
         <v>Humanities</v>
@@ -4501,7 +4501,7 @@
         <v>Twelve</v>
       </c>
       <c r="F158" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G158" t="str">
         <v>Humanities</v>
@@ -4527,7 +4527,7 @@
         <v>Twelve</v>
       </c>
       <c r="F159" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G159" t="str">
         <v>Humanities</v>
@@ -4553,7 +4553,7 @@
         <v>Twelve</v>
       </c>
       <c r="F160" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G160" t="str">
         <v>Humanities</v>
@@ -4579,7 +4579,7 @@
         <v>Twelve</v>
       </c>
       <c r="F161" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G161" t="str">
         <v>Humanities</v>
@@ -4605,7 +4605,7 @@
         <v>Twelve</v>
       </c>
       <c r="F162" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G162" t="str">
         <v>Humanities</v>
@@ -4631,7 +4631,7 @@
         <v>Twelve</v>
       </c>
       <c r="F163" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G163" t="str">
         <v>Humanities</v>
@@ -4657,7 +4657,7 @@
         <v>Twelve</v>
       </c>
       <c r="F164" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G164" t="str">
         <v>Humanities</v>
@@ -4683,7 +4683,7 @@
         <v>Twelve</v>
       </c>
       <c r="F165" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G165" t="str">
         <v>Humanities</v>
@@ -4709,7 +4709,7 @@
         <v>Twelve</v>
       </c>
       <c r="F166" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G166" t="str">
         <v>Humanities</v>
@@ -4735,7 +4735,7 @@
         <v>Twelve</v>
       </c>
       <c r="F167" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G167" t="str">
         <v>Humanities</v>
@@ -4761,7 +4761,7 @@
         <v>Twelve</v>
       </c>
       <c r="F168" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G168" t="str">
         <v>Humanities</v>
@@ -4787,7 +4787,7 @@
         <v>Twelve</v>
       </c>
       <c r="F169" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G169" t="str">
         <v>Humanities</v>
@@ -4813,7 +4813,7 @@
         <v>Twelve</v>
       </c>
       <c r="F170" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G170" t="str">
         <v>Humanities</v>
@@ -4839,7 +4839,7 @@
         <v>Twelve</v>
       </c>
       <c r="F171" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G171" t="str">
         <v>Humanities</v>
@@ -4865,7 +4865,7 @@
         <v>Twelve</v>
       </c>
       <c r="F172" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G172" t="str">
         <v>Humanities</v>
@@ -4891,7 +4891,7 @@
         <v>Twelve</v>
       </c>
       <c r="F173" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G173" t="str">
         <v>Humanities</v>
@@ -4917,7 +4917,7 @@
         <v>Twelve</v>
       </c>
       <c r="F174" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G174" t="str">
         <v>Humanities</v>
@@ -4943,7 +4943,7 @@
         <v>Twelve</v>
       </c>
       <c r="F175" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G175" t="str">
         <v>Humanities</v>
@@ -4969,7 +4969,7 @@
         <v>Twelve</v>
       </c>
       <c r="F176" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G176" t="str">
         <v>Humanities</v>
@@ -4995,7 +4995,7 @@
         <v>Twelve</v>
       </c>
       <c r="F177" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G177" t="str">
         <v>Humanities</v>
@@ -5021,7 +5021,7 @@
         <v>Twelve</v>
       </c>
       <c r="F178" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G178" t="str">
         <v>Humanities</v>
@@ -5047,7 +5047,7 @@
         <v>Twelve</v>
       </c>
       <c r="F179" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G179" t="str">
         <v>Humanities</v>
@@ -5073,7 +5073,7 @@
         <v>Twelve</v>
       </c>
       <c r="F180" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G180" t="str">
         <v>Humanities</v>
@@ -5099,7 +5099,7 @@
         <v>Twelve</v>
       </c>
       <c r="F181" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G181" t="str">
         <v>Humanities</v>
@@ -5125,7 +5125,7 @@
         <v>Twelve</v>
       </c>
       <c r="F182" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G182" t="str">
         <v>Humanities</v>
@@ -6971,13 +6971,16 @@
         <v>Eleven</v>
       </c>
       <c r="F253" t="str">
-        <v>Rupsa</v>
+        <v>Rupsha</v>
       </c>
       <c r="G253" t="str">
         <v>Science</v>
       </c>
       <c r="H253" t="str">
         <v>Male</v>
+      </c>
+      <c r="I253" t="str">
+        <v/>
       </c>
     </row>
     <row r="254">
@@ -9779,7 +9782,7 @@
         <v>Eleven</v>
       </c>
       <c r="F361" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G361" t="str">
         <v>Humanities</v>
@@ -9805,7 +9808,7 @@
         <v>Eleven</v>
       </c>
       <c r="F362" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G362" t="str">
         <v>Humanities</v>
@@ -9831,7 +9834,7 @@
         <v>Eleven</v>
       </c>
       <c r="F363" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G363" t="str">
         <v>Humanities</v>
@@ -9857,7 +9860,7 @@
         <v>Eleven</v>
       </c>
       <c r="F364" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G364" t="str">
         <v>Humanities</v>
@@ -9883,7 +9886,7 @@
         <v>Eleven</v>
       </c>
       <c r="F365" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G365" t="str">
         <v>Humanities</v>
@@ -9909,7 +9912,7 @@
         <v>Eleven</v>
       </c>
       <c r="F366" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G366" t="str">
         <v>Humanities</v>
@@ -9935,7 +9938,7 @@
         <v>Eleven</v>
       </c>
       <c r="F367" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G367" t="str">
         <v>Humanities</v>
@@ -9961,7 +9964,7 @@
         <v>Eleven</v>
       </c>
       <c r="F368" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G368" t="str">
         <v>Humanities</v>
@@ -9987,7 +9990,7 @@
         <v>Eleven</v>
       </c>
       <c r="F369" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G369" t="str">
         <v>Humanities</v>
@@ -10013,7 +10016,7 @@
         <v>Eleven</v>
       </c>
       <c r="F370" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G370" t="str">
         <v>Humanities</v>
@@ -10039,7 +10042,7 @@
         <v>Eleven</v>
       </c>
       <c r="F371" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G371" t="str">
         <v>Humanities</v>
@@ -10065,7 +10068,7 @@
         <v>Eleven</v>
       </c>
       <c r="F372" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G372" t="str">
         <v>Humanities</v>
@@ -10091,7 +10094,7 @@
         <v>Eleven</v>
       </c>
       <c r="F373" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G373" t="str">
         <v>Humanities</v>
@@ -10117,7 +10120,7 @@
         <v>Eleven</v>
       </c>
       <c r="F374" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G374" t="str">
         <v>Humanities</v>
@@ -10143,7 +10146,7 @@
         <v>Eleven</v>
       </c>
       <c r="F375" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G375" t="str">
         <v>Humanities</v>
@@ -10169,7 +10172,7 @@
         <v>Eleven</v>
       </c>
       <c r="F376" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G376" t="str">
         <v>Humanities</v>
@@ -10195,7 +10198,7 @@
         <v>Eleven</v>
       </c>
       <c r="F377" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G377" t="str">
         <v>Humanities</v>
@@ -10221,7 +10224,7 @@
         <v>Eleven</v>
       </c>
       <c r="F378" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G378" t="str">
         <v>Humanities</v>
@@ -10247,7 +10250,7 @@
         <v>Eleven</v>
       </c>
       <c r="F379" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G379" t="str">
         <v>Humanities</v>
@@ -10273,7 +10276,7 @@
         <v>Eleven</v>
       </c>
       <c r="F380" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G380" t="str">
         <v>Humanities</v>
@@ -10299,7 +10302,7 @@
         <v>Eleven</v>
       </c>
       <c r="F381" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G381" t="str">
         <v>Humanities</v>
@@ -10325,7 +10328,7 @@
         <v>Eleven</v>
       </c>
       <c r="F382" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G382" t="str">
         <v>Humanities</v>
@@ -10351,7 +10354,7 @@
         <v>Eleven</v>
       </c>
       <c r="F383" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G383" t="str">
         <v>Humanities</v>
@@ -10377,7 +10380,7 @@
         <v>Eleven</v>
       </c>
       <c r="F384" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G384" t="str">
         <v>Humanities</v>
@@ -10403,7 +10406,7 @@
         <v>Eleven</v>
       </c>
       <c r="F385" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G385" t="str">
         <v>Humanities</v>
@@ -10429,7 +10432,7 @@
         <v>Eleven</v>
       </c>
       <c r="F386" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G386" t="str">
         <v>Humanities</v>
@@ -10455,7 +10458,7 @@
         <v>Eleven</v>
       </c>
       <c r="F387" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G387" t="str">
         <v>Humanities</v>
@@ -10481,7 +10484,7 @@
         <v>Eleven</v>
       </c>
       <c r="F388" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G388" t="str">
         <v>Humanities</v>
@@ -10507,7 +10510,7 @@
         <v>Eleven</v>
       </c>
       <c r="F389" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G389" t="str">
         <v>Humanities</v>
@@ -10533,7 +10536,7 @@
         <v>Eleven</v>
       </c>
       <c r="F390" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G390" t="str">
         <v>Humanities</v>
@@ -10559,7 +10562,7 @@
         <v>Eleven</v>
       </c>
       <c r="F391" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G391" t="str">
         <v>Humanities</v>
@@ -10585,7 +10588,7 @@
         <v>Eleven</v>
       </c>
       <c r="F392" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G392" t="str">
         <v>Humanities</v>
@@ -10611,7 +10614,7 @@
         <v>Eleven</v>
       </c>
       <c r="F393" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G393" t="str">
         <v>Humanities</v>
@@ -10637,7 +10640,7 @@
         <v>Eleven</v>
       </c>
       <c r="F394" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G394" t="str">
         <v>Humanities</v>
@@ -10663,7 +10666,7 @@
         <v>Eleven</v>
       </c>
       <c r="F395" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G395" t="str">
         <v>Humanities</v>
@@ -10689,7 +10692,7 @@
         <v>Eleven</v>
       </c>
       <c r="F396" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G396" t="str">
         <v>Humanities</v>
@@ -10715,7 +10718,7 @@
         <v>Eleven</v>
       </c>
       <c r="F397" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G397" t="str">
         <v>Humanities</v>
@@ -10741,7 +10744,7 @@
         <v>Eleven</v>
       </c>
       <c r="F398" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G398" t="str">
         <v>Humanities</v>
@@ -10767,7 +10770,7 @@
         <v>Eleven</v>
       </c>
       <c r="F399" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G399" t="str">
         <v>Humanities</v>
@@ -10793,7 +10796,7 @@
         <v>Eleven</v>
       </c>
       <c r="F400" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G400" t="str">
         <v>Humanities</v>
@@ -10819,7 +10822,7 @@
         <v>Eleven</v>
       </c>
       <c r="F401" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G401" t="str">
         <v>Humanities</v>
@@ -10845,7 +10848,7 @@
         <v>Eleven</v>
       </c>
       <c r="F402" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G402" t="str">
         <v>Humanities</v>
@@ -10871,7 +10874,7 @@
         <v>Eleven</v>
       </c>
       <c r="F403" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G403" t="str">
         <v>Humanities</v>
@@ -10897,7 +10900,7 @@
         <v>Eleven</v>
       </c>
       <c r="F404" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G404" t="str">
         <v>Humanities</v>
@@ -10923,7 +10926,7 @@
         <v>Eleven</v>
       </c>
       <c r="F405" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G405" t="str">
         <v>Humanities</v>
@@ -10949,7 +10952,7 @@
         <v>Eleven</v>
       </c>
       <c r="F406" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G406" t="str">
         <v>Humanities</v>
@@ -10975,7 +10978,7 @@
         <v>Eleven</v>
       </c>
       <c r="F407" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G407" t="str">
         <v>Humanities</v>
@@ -11001,7 +11004,7 @@
         <v>Eleven</v>
       </c>
       <c r="F408" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G408" t="str">
         <v>Humanities</v>
@@ -11027,7 +11030,7 @@
         <v>Eleven</v>
       </c>
       <c r="F409" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G409" t="str">
         <v>Humanities</v>
@@ -11053,7 +11056,7 @@
         <v>Eleven</v>
       </c>
       <c r="F410" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G410" t="str">
         <v>Humanities</v>
@@ -11079,7 +11082,7 @@
         <v>Eleven</v>
       </c>
       <c r="F411" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G411" t="str">
         <v>Humanities</v>
@@ -11105,7 +11108,7 @@
         <v>Eleven</v>
       </c>
       <c r="F412" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G412" t="str">
         <v>Humanities</v>
@@ -11131,7 +11134,7 @@
         <v>Eleven</v>
       </c>
       <c r="F413" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G413" t="str">
         <v>Humanities</v>
@@ -11157,7 +11160,7 @@
         <v>Eleven</v>
       </c>
       <c r="F414" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G414" t="str">
         <v>Humanities</v>
@@ -11183,7 +11186,7 @@
         <v>Eleven</v>
       </c>
       <c r="F415" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G415" t="str">
         <v>Humanities</v>
@@ -11209,7 +11212,7 @@
         <v>Eleven</v>
       </c>
       <c r="F416" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G416" t="str">
         <v>Humanities</v>
@@ -11235,7 +11238,7 @@
         <v>Eleven</v>
       </c>
       <c r="F417" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G417" t="str">
         <v>Humanities</v>
@@ -11261,7 +11264,7 @@
         <v>Eleven</v>
       </c>
       <c r="F418" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G418" t="str">
         <v>Humanities</v>
@@ -11287,7 +11290,7 @@
         <v>Eleven</v>
       </c>
       <c r="F419" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G419" t="str">
         <v>Humanities</v>
@@ -11313,7 +11316,7 @@
         <v>Eleven</v>
       </c>
       <c r="F420" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G420" t="str">
         <v>Humanities</v>
@@ -11339,7 +11342,7 @@
         <v>Eleven</v>
       </c>
       <c r="F421" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G421" t="str">
         <v>Humanities</v>
@@ -11365,7 +11368,7 @@
         <v>Eleven</v>
       </c>
       <c r="F422" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G422" t="str">
         <v>Humanities</v>
@@ -11391,7 +11394,7 @@
         <v>Eleven</v>
       </c>
       <c r="F423" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G423" t="str">
         <v>Humanities</v>
@@ -11417,7 +11420,7 @@
         <v>Eleven</v>
       </c>
       <c r="F424" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G424" t="str">
         <v>Humanities</v>
@@ -11443,7 +11446,7 @@
         <v>Eleven</v>
       </c>
       <c r="F425" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G425" t="str">
         <v>Humanities</v>
@@ -11469,7 +11472,7 @@
         <v>Eleven</v>
       </c>
       <c r="F426" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G426" t="str">
         <v>Humanities</v>
@@ -11495,7 +11498,7 @@
         <v>Eleven</v>
       </c>
       <c r="F427" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G427" t="str">
         <v>Humanities</v>
@@ -11521,7 +11524,7 @@
         <v>Eleven</v>
       </c>
       <c r="F428" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G428" t="str">
         <v>Humanities</v>
@@ -11547,7 +11550,7 @@
         <v>Eleven</v>
       </c>
       <c r="F429" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G429" t="str">
         <v>Humanities</v>
@@ -11573,7 +11576,7 @@
         <v>Eleven</v>
       </c>
       <c r="F430" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G430" t="str">
         <v>Humanities</v>
@@ -11599,7 +11602,7 @@
         <v>Eleven</v>
       </c>
       <c r="F431" t="str">
-        <v>Shitalakshya</v>
+        <v>Shitalakhya</v>
       </c>
       <c r="G431" t="str">
         <v>Humanities</v>
@@ -13836,9 +13839,328 @@
         <v/>
       </c>
     </row>
+    <row r="517">
+      <c r="A517" t="str">
+        <v>251042</v>
+      </c>
+      <c r="B517" t="str">
+        <v>214</v>
+      </c>
+      <c r="C517" t="str">
+        <v>MAHBUBA ZARIN TASMI</v>
+      </c>
+      <c r="D517" t="str">
+        <v>2025-26</v>
+      </c>
+      <c r="E517" t="str">
+        <v>Eleven</v>
+      </c>
+      <c r="F517" t="str">
+        <v>Madhumati</v>
+      </c>
+      <c r="G517" t="str">
+        <v>Science</v>
+      </c>
+      <c r="H517" t="str">
+        <v>Female</v>
+      </c>
+      <c r="I517" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="str">
+        <v>251131</v>
+      </c>
+      <c r="B518" t="str">
+        <v>255</v>
+      </c>
+      <c r="C518" t="str">
+        <v>FARHINA TABASSOM ANI</v>
+      </c>
+      <c r="D518" t="str">
+        <v>2025-26</v>
+      </c>
+      <c r="E518" t="str">
+        <v>Eleven</v>
+      </c>
+      <c r="F518" t="str">
+        <v>Madhumati</v>
+      </c>
+      <c r="G518" t="str">
+        <v>Science</v>
+      </c>
+      <c r="H518" t="str">
+        <v>Female</v>
+      </c>
+      <c r="I518" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="str">
+        <v>251203</v>
+      </c>
+      <c r="B519" t="str">
+        <v>258</v>
+      </c>
+      <c r="C519" t="str">
+        <v>MD ROKIB SHIKDER ROKI</v>
+      </c>
+      <c r="D519" t="str">
+        <v>2025-26</v>
+      </c>
+      <c r="E519" t="str">
+        <v>Eleven</v>
+      </c>
+      <c r="F519" t="str">
+        <v>Madhumati</v>
+      </c>
+      <c r="G519" t="str">
+        <v>Science</v>
+      </c>
+      <c r="H519" t="str">
+        <v>Male</v>
+      </c>
+      <c r="I519" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="str">
+        <v>251205</v>
+      </c>
+      <c r="B520" t="str">
+        <v>259</v>
+      </c>
+      <c r="C520" t="str">
+        <v>ROHAN SIKDER CHONCHAL</v>
+      </c>
+      <c r="D520" t="str">
+        <v>2025-26</v>
+      </c>
+      <c r="E520" t="str">
+        <v>Eleven</v>
+      </c>
+      <c r="F520" t="str">
+        <v>Madhumati</v>
+      </c>
+      <c r="G520" t="str">
+        <v>Science</v>
+      </c>
+      <c r="H520" t="str">
+        <v>Male</v>
+      </c>
+      <c r="I520" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="str">
+        <v>251032</v>
+      </c>
+      <c r="B521" t="str">
+        <v>313</v>
+      </c>
+      <c r="C521" t="str">
+        <v>MD ALI NEWAS SOHAN</v>
+      </c>
+      <c r="D521" t="str">
+        <v>2025-26</v>
+      </c>
+      <c r="E521" t="str">
+        <v>Eleven</v>
+      </c>
+      <c r="F521" t="str">
+        <v>Rupsha</v>
+      </c>
+      <c r="G521" t="str">
+        <v>Science</v>
+      </c>
+      <c r="H521" t="str">
+        <v>Male</v>
+      </c>
+      <c r="I521" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="str">
+        <v>251210</v>
+      </c>
+      <c r="B522" t="str">
+        <v>334</v>
+      </c>
+      <c r="C522" t="str">
+        <v>PIAS SARKER APON</v>
+      </c>
+      <c r="D522" t="str">
+        <v>2025-26</v>
+      </c>
+      <c r="E522" t="str">
+        <v>Eleven</v>
+      </c>
+      <c r="F522" t="str">
+        <v>Rupsha</v>
+      </c>
+      <c r="G522" t="str">
+        <v>Science</v>
+      </c>
+      <c r="H522" t="str">
+        <v>Male</v>
+      </c>
+      <c r="I522" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="str">
+        <v>251270</v>
+      </c>
+      <c r="B523" t="str">
+        <v>883</v>
+      </c>
+      <c r="C523" t="str">
+        <v>MST UMME RUBIYA FATIMA</v>
+      </c>
+      <c r="D523" t="str">
+        <v>2025-26</v>
+      </c>
+      <c r="E523" t="str">
+        <v>Eleven</v>
+      </c>
+      <c r="F523" t="str">
+        <v>Shitalakhya</v>
+      </c>
+      <c r="G523" t="str">
+        <v>Humanities</v>
+      </c>
+      <c r="H523" t="str">
+        <v>Female</v>
+      </c>
+      <c r="I523" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="str">
+        <v>251005</v>
+      </c>
+      <c r="B524" t="str">
+        <v>884</v>
+      </c>
+      <c r="C524" t="str">
+        <v>MD PAVEL SHEIKH</v>
+      </c>
+      <c r="D524" t="str">
+        <v>2025-26</v>
+      </c>
+      <c r="E524" t="str">
+        <v>Eleven</v>
+      </c>
+      <c r="F524" t="str">
+        <v>Shitalakhya</v>
+      </c>
+      <c r="G524" t="str">
+        <v>Humanities</v>
+      </c>
+      <c r="H524" t="str">
+        <v>Male</v>
+      </c>
+      <c r="I524" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="str">
+        <v>250938</v>
+      </c>
+      <c r="B525" t="str">
+        <v>886</v>
+      </c>
+      <c r="C525" t="str">
+        <v>MD ABUZAR HRIDOY</v>
+      </c>
+      <c r="D525" t="str">
+        <v>2025-26</v>
+      </c>
+      <c r="E525" t="str">
+        <v>Eleven</v>
+      </c>
+      <c r="F525" t="str">
+        <v>Shitalakhya</v>
+      </c>
+      <c r="G525" t="str">
+        <v>Humanities</v>
+      </c>
+      <c r="H525" t="str">
+        <v>Male</v>
+      </c>
+      <c r="I525" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="str">
+        <v>24072026454</v>
+      </c>
+      <c r="B526" t="str">
+        <v>832</v>
+      </c>
+      <c r="C526" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="D526" t="str">
+        <v>2025-26</v>
+      </c>
+      <c r="E526" t="str">
+        <v>Eleven</v>
+      </c>
+      <c r="F526" t="str">
+        <v>Shitalakhya</v>
+      </c>
+      <c r="G526" t="str">
+        <v>Humanities</v>
+      </c>
+      <c r="H526" t="str">
+        <v>Male</v>
+      </c>
+      <c r="I526" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="str">
+        <v>24072026455</v>
+      </c>
+      <c r="B527" t="str">
+        <v>885</v>
+      </c>
+      <c r="C527" t="str">
+        <v>unknown2</v>
+      </c>
+      <c r="D527" t="str">
+        <v>2025-26</v>
+      </c>
+      <c r="E527" t="str">
+        <v>Eleven</v>
+      </c>
+      <c r="F527" t="str">
+        <v>Shitalakhya</v>
+      </c>
+      <c r="G527" t="str">
+        <v>Humanities</v>
+      </c>
+      <c r="H527" t="str">
+        <v>Male</v>
+      </c>
+      <c r="I527" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I516"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I527"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/uploads/student-bank.xlsx
+++ b/uploads/student-bank.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I527"/>
+  <dimension ref="A1:I528"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -14158,9 +14158,38 @@
         <v/>
       </c>
     </row>
+    <row r="528">
+      <c r="A528" t="str">
+        <v>251091</v>
+      </c>
+      <c r="B528" t="str">
+        <v>832</v>
+      </c>
+      <c r="C528" t="str">
+        <v>Md. Riduan Kabir Nabil</v>
+      </c>
+      <c r="D528" t="str">
+        <v>2025-26</v>
+      </c>
+      <c r="E528" t="str">
+        <v>Eleven</v>
+      </c>
+      <c r="F528" t="str">
+        <v>Shitalakhya</v>
+      </c>
+      <c r="G528" t="str">
+        <v>Humanities</v>
+      </c>
+      <c r="H528" t="str">
+        <v>Male</v>
+      </c>
+      <c r="I528" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I527"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I528"/>
   </ignoredErrors>
 </worksheet>
 </file>